--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C53233E-C0A9-4111-982C-791F7E93A377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1FA8A4-206A-4594-8DBB-AF1FFDE0AAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5925" yWindow="750" windowWidth="21585" windowHeight="14370" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
+    <workbookView xWindow="-22815" yWindow="1335" windowWidth="21585" windowHeight="14370" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,11 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="91">
-  <si>
-    <t>項次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="141">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,10 +73,6 @@
   </si>
   <si>
     <t>Targus 藍芽無線立體聲耳機麥克風AEH104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Sekc 真無線藍芽耳機SBT-T6 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -130,10 +122,6 @@
   </si>
   <si>
     <t>力回饋方向盤2.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全新拆封 發現家裡不適合  已組裝好 免安裝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -211,15 +199,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>全新未拆封</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>沒時間玩了QQ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sekc 真無線藍芽耳機.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -339,21 +319,6 @@
   </si>
   <si>
     <t>參考
-https://tzuhui99.pixnet.net/blog/posts/4044227046</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>參考
-https://www.minipbigp.com/blog/2680/srv-a11/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>參考
-https://www.sansuitw.com/products/sansui-spj-wd-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>參考
 https://24h.pchome.com.tw/prod/DEBB52-A900C21DO
 https://tw.transcend-info.com/product/dashcam/drivepro-20</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -431,12 +396,624 @@
 https://www.masalife.tw/products/joy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>B.FRiEND CK1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND CK12.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND CK13.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND CK14.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND KB700-Pro.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND KB700-Pro2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND KB700-Pro3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND KB700-Pro4.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POJUN PJ02.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POJUN PJ022.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POJUN PJ023.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POJUN PJ024.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POJUN PJ02 粉白色 機械式鍵盤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND KB700-Pro 鋁合金薄型鍵盤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>●簡約外觀、俐落有型
+●高規格剪刀腳按鍵結構
+●如此輕巧，僅有0.53 kg
+●超薄機身，厚度薄至1.6cm
+●圓潤凹陷造型鍵帽，大幅提升精準度及舒適度
+●支援雙系統，一鍵切換win/ios
+官方介紹：
+http://www.b-friendit.com/web/product/office_in.jsp?pd_no=PD1605779107279</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>材質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>鋁合金上蓋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>髮絲紋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>軸承</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:KAILH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>凱華軸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>-5000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>萬次點擊壽命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>顏色搭配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>顆粉色鍵帽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>顆白色鍵帽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>💖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>燈光效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>種燈光效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>組自訂義</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+🎁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>贈送一套相反配色鍵帽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自由搭配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+官方介紹：
+https://www.pojunshop.com/products/pj02-%E7%B2%89%E7%99%BD%E6%A9%9F%E6%A2%B0%E5%BC%8F%E9%8D%B5%E7%9B%A4?srsltid=AfmBOoq4HFZmx_1_BgksTVqIMnXOo4-vfcgdEfCQX6pgq3NC6OzCW24n</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.FRiEND CK1 機械光軸有線鍵盤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>● 光軸按鍵
+● 超高壽命
+● 全區無衝突防鬼
+● 鋁合金上蓋
+● 炫彩按鍵及邊框燈效
+● 防潑水
+官方介紹：
+http://www.b-friendit.com/web/product/product_in.jsp?pd_no=PD1580882496559</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>● 清脆光軸 / 靜音光軸，雙版本可選
+● 二次射出透光鍵帽
+● 專用軟體可提供巨集、燈效設定
+● 100% 全區域不衝突防鬼鍵
+● RGB炫彩背光
+● 航空級鋁合金面板
+● 編織線材 / 鍍金接頭
+● 淺顯易懂LED指示燈
+● 大面積底部止滑墊
+官方介紹：
+https://www.powzan.com/web/product/product_in.jsp?pd_no=PD1617847990865</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWZAN  CK650 RGB光學機械遊戲鍵盤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWZAN CK650.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWZAN CK6502.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWZAN CK6503.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POWZAN CK6504.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BenQ 55SY700 55型 4K HDR護眼大型液晶顯示器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benq55SY700.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benq55SY7002.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benq55SY7003.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benq55SY7004.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">需自取(捷運台北橋站斜對面)
+參考
+https://www.trustworthy.com.tw/productIntroduce.php?sku=MOBQ55SY700
+https://www.qkshopping.com.tw/product/55sy700
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alloy Elite RGB 有線機械式電競鍵盤 Cherry MX Brown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全新
+參考
+https://buy.gamer.com.tw/atmItem.php?sn=24253&amp;srsltid=AfmBOoqYAU-xZEVb8PN1R5O6KWdMFeNB8hhFamyFWR8gzRe9XdpTCZla
+https://www.youtube.com/watch?v=CZhMjWtWLCA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HyperX Alloy Elite.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Haier 雙層防燙多功能智能美食鍋、附蒸架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Haier美食鍋.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>義大利Giaretti 復古造型 麵包機 GT-OT10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Giaretti 復古造型 麵包機2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Giaretti 復古造型 麵包機3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KINYO雙電壓旅行快煮壼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KINYO雙電壓旅行快煮壼.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kolin 歌林 研磨冰沙調理機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kolin 歌林 研磨冰沙調理機2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kolin 歌林 研磨冰沙調理機.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需自取(五股衛生所)
+全新拆封 發現家裡不適合  已組裝好 免安裝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUOCO大寶鍋T4 Gold鈦晶岩不沾鍋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUOCO大寶鍋T4 Gold鈦晶岩不沾鍋.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考
+https://www.gukang.com.tw/products/ad2002a134gymn4106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUOCO 多功能方鍋.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUOCO 多功能方鍋2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CUOCO 多功能方鍋 鈦金陶瓷IH不沾鍋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙電壓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考
+https://shopee.tw/product/799860217/22672104482</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考
+https://www.minipbigp.com/blog/2680/srv-a11/
+https://www.tw.coupang.com/products/SRV-A11-WIFI-%E6%99%BA%E8%83%BD%E6%8E%83%E6%8B%96%E6%8E%83%E5%9C%B0%E6%A9%9F%E5%99%A8%E4%BA%BA-%E9%80%81%E4%B8%80%E5%B9%B4%E8%80%97%E6%9D%90-32-x-32-x-8cm-2.6kg-400ml%2C-1%E5%80%8B-463112410972161</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>參考
+https://tw.buy.yahoo.com/gdsale/SANSUI-%E5%B1%B1%E6%B0%B4-%E8%A1%8C%E5%8B%95%E5%AE%89%E5%8D%93-1080P-WIFI-%E8%87%AA%E5%8B%95%E5%B0%8D%E7%84%A6-%E7%84%A1%E7%B7%9A%E5%BE%AE%E5%9E%8B%E6%8A%95%E5%BD%B1%E6%A9%9F-SPJ-WD-10883879.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下殺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Giaretti 復古造型 麵包機.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -451,6 +1028,18 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -796,439 +1385,720 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE215CEF-0362-4ABB-BECD-48602F7139CF}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.5" customWidth="1"/>
-    <col min="4" max="4" width="49.125" customWidth="1"/>
-    <col min="5" max="5" width="19.125" customWidth="1"/>
-    <col min="6" max="6" width="20.125" customWidth="1"/>
+    <col min="5" max="5" width="49.125" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2">
+        <v>650</v>
+      </c>
+      <c r="F2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3">
+        <v>1300</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4">
+        <v>900</v>
+      </c>
+      <c r="E4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5">
+        <v>400</v>
+      </c>
+      <c r="E5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6">
+        <v>550</v>
+      </c>
+      <c r="E6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7">
+        <v>350</v>
+      </c>
+      <c r="F7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9">
+        <v>2800</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="219" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13">
+        <v>1100</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>1100</v>
+      </c>
+      <c r="D14">
+        <v>900</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>300</v>
+      </c>
+      <c r="D15">
+        <v>150</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>1100</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C16" s="1">
+        <v>9000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="198" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>900</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D18" s="1">
+        <v>700</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="66" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>7000</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3500</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>300</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>600</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1">
+        <v>4000</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1600</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1">
+        <v>700</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1">
+        <v>32000</v>
+      </c>
+      <c r="D26" s="1">
+        <v>23000</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D27" s="1">
+        <v>800</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D28" s="1">
+        <v>800</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="99" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="1">
+        <v>4500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2800</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4000</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2500</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="1">
+        <v>700</v>
+      </c>
+      <c r="D31" s="1">
+        <v>500</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="1">
         <v>7500</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>800</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="D32" s="1">
+        <v>5500</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="1">
+        <v>12000</v>
+      </c>
+      <c r="D33" s="1">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="1">
         <v>4000</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="1">
-        <v>800</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2800</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1200</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1600</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1100</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1">
-        <v>700</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="D34" s="1">
+        <v>2500</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2000</v>
+      </c>
+      <c r="D35" s="1">
+        <v>900</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="1">
+        <v>3780</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1800</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="1">
+        <v>970</v>
+      </c>
+      <c r="D37" s="1">
+        <v>650</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="1">
+        <v>6000</v>
+      </c>
+      <c r="D38" s="1">
         <v>3000</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1">
-        <v>25000</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="1">
-        <v>800</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="99" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2500</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="1">
-        <v>500</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="1">
-        <v>7000</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="1">
-        <v>6000</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" ht="66" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="F38" t="s">
         <v>75</v>
       </c>
-      <c r="E25" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+    </row>
+    <row r="39" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="1">
-        <v>700</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="C39" s="1">
+        <v>4800</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3800</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" t="s">
         <v>78</v>
-      </c>
-      <c r="E26" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="1">
-        <v>5000</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="1">
-        <v>4000</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1FA8A4-206A-4594-8DBB-AF1FFDE0AAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124A2FB6-CF34-43AA-89CD-98307F7FA324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22815" yWindow="1335" windowWidth="21585" windowHeight="14370" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
+    <workbookView xWindow="-25635" yWindow="1080" windowWidth="21585" windowHeight="14370" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="146">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1006,6 +1006,29 @@
   </si>
   <si>
     <t>Giaretti 復古造型 麵包機.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大家源 手持無線吸塵器 TVC-230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大家源 手持無線吸塵器 TVC-230.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大家源 手持無線吸塵器 TVC-2302.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大家源 手持無線吸塵器 TVC-2303.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僅使用一次
+本來要放車上，但放車上又覺的太大
+官網：
+https://www.tcylife.net/SalePage/Index/11391731</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1385,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE215CEF-0362-4ABB-BECD-48602F7139CF}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -1415,689 +1438,709 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2">
+        <v>1600</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>133</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>650</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>131</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>128</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>1300</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4">
-        <v>900</v>
-      </c>
-      <c r="E4" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>125</v>
+      </c>
+      <c r="G5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7">
+        <v>550</v>
+      </c>
+      <c r="E7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>116</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>350</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="132" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8">
-        <v>4000</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H8" t="s">
-        <v>110</v>
-      </c>
-      <c r="I8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9">
+        <v>4000</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>113</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>2800</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="11" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>102</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>1500</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" t="s">
         <v>103</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G11" t="s">
         <v>104</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>105</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="219" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="12" spans="1:9" ht="219" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>95</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>1000</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>91</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G12" t="s">
         <v>92</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H12" t="s">
         <v>93</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I12" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12">
-        <v>1100</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C13">
         <v>1100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="C14">
         <v>1100</v>
       </c>
-      <c r="D14">
+      <c r="E14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>1100</v>
+      </c>
+      <c r="D15">
         <v>900</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>300</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>150</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>15</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+    <row r="17" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C17" s="1">
         <v>9000</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17" s="1">
         <v>4500</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="198" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
+    <row r="18" spans="2:8" ht="198" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C18" s="1">
         <v>1200</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>900</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="1" t="s">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C19" s="1">
         <v>1000</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D19" s="1">
         <v>700</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>20</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="66" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
+    <row r="20" spans="2:8" ht="66" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C20" s="1">
         <v>7000</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>3500</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F20" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D20" s="1">
-        <v>600</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C21" s="1">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="D21" s="1">
-        <v>2500</v>
+        <v>600</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="H21" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1">
-        <v>1200</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>4000</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2500</v>
+      </c>
       <c r="E22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="1">
-        <v>700</v>
+        <v>1600</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1">
-        <v>3000</v>
+        <v>700</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" t="s">
         <v>33</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
+    <row r="27" spans="2:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C27" s="1">
         <v>32000</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>23000</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>35</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
+    <row r="28" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C28" s="1">
         <v>3000</v>
-      </c>
-      <c r="D27" s="1">
-        <v>800</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1500</v>
       </c>
       <c r="D28" s="1">
         <v>800</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>800</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="99" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
+    <row r="30" spans="2:8" ht="99" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C30" s="1">
         <v>4500</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D30" s="1">
         <v>2800</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" s="1">
-        <v>4000</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2500</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="1">
+        <v>4000</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2500</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C32" s="1">
         <v>700</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>500</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F32" t="s">
         <v>56</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G32" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
+    <row r="33" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C33" s="1">
         <v>7500</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D33" s="1">
         <v>5500</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="148.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
+    <row r="34" spans="2:6" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C34" s="1">
         <v>12000</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D34" s="1">
         <v>6000</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="165" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
+    <row r="35" spans="2:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C35" s="1">
         <v>4000</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D35" s="1">
         <v>2500</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C36" s="1">
         <v>2000</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D36" s="1">
         <v>900</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F36" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="66" x14ac:dyDescent="0.25">
-      <c r="B36" s="1" t="s">
+    <row r="37" spans="2:6" ht="66" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C37" s="1">
         <v>3780</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D37" s="1">
         <v>1800</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E37" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="33" x14ac:dyDescent="0.25">
-      <c r="B37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" s="1">
-        <v>970</v>
-      </c>
-      <c r="D37" s="1">
-        <v>650</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="1">
+        <v>970</v>
+      </c>
+      <c r="D38" s="1">
+        <v>650</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C39" s="1">
         <v>6000</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D39" s="1">
         <v>3000</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
+    <row r="40" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C40" s="1">
         <v>4800</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D40" s="1">
         <v>3800</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F40" t="s">
         <v>78</v>
       </c>
     </row>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124A2FB6-CF34-43AA-89CD-98307F7FA324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97770519-CD24-4379-8A09-2100E9D8E4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25635" yWindow="1080" windowWidth="21585" windowHeight="14370" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="140">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -860,34 +860,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BenQ 55SY700 55型 4K HDR護眼大型液晶顯示器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Benq55SY700.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Benq55SY7002.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Benq55SY7003.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Benq55SY7004.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">需自取(捷運台北橋站斜對面)
-參考
-https://www.trustworthy.com.tw/productIntroduce.php?sku=MOBQ55SY700
-https://www.qkshopping.com.tw/product/55sy700
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Alloy Elite RGB 有線機械式電競鍵盤 Cherry MX Brown</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -947,11 +919,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需自取(五股衛生所)
-全新拆封 發現家裡不適合  已組裝好 免安裝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CUOCO大寶鍋T4 Gold鈦晶岩不沾鍋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1029,6 +996,11 @@
 本來要放車上，但放車上又覺的太大
 官網：
 https://www.tcylife.net/SalePage/Index/11391731</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需自取(五股衛生所附近)
+全新拆封 發現家裡不適合  已組裝好 免安裝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1408,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE215CEF-0362-4ABB-BECD-48602F7139CF}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -1420,7 +1392,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1429,7 +1401,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1440,22 +1412,22 @@
     </row>
     <row r="2" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C2">
         <v>1600</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1463,92 +1435,95 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>650</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C4">
         <v>1300</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C5">
         <v>900</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>400</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C7">
         <v>550</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0</v>
+      </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>350</v>
       </c>
       <c r="F8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.25">
@@ -1556,591 +1531,568 @@
         <v>107</v>
       </c>
       <c r="C9">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" t="s">
         <v>109</v>
       </c>
-      <c r="H9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C10">
-        <v>2800</v>
+        <v>1500</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="G10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="219" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C11">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="219" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C13">
         <v>1100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>1100</v>
       </c>
+      <c r="D14">
+        <v>900</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="D15">
+        <v>150</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>9000</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="198" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D17" s="1">
         <v>900</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16">
-        <v>300</v>
-      </c>
-      <c r="D16">
-        <v>150</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1">
-        <v>9000</v>
-      </c>
-      <c r="D17" s="1">
-        <v>4500</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="198" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="66" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1">
+        <v>7000</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3500</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
         <v>1000</v>
       </c>
-      <c r="D19" s="1">
-        <v>700</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="66" x14ac:dyDescent="0.25">
-      <c r="B20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1">
-        <v>7000</v>
-      </c>
       <c r="D20" s="1">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D21" s="1">
-        <v>600</v>
+        <v>2500</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1">
-        <v>4000</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2500</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="1">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="165" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1">
+        <v>32000</v>
+      </c>
+      <c r="D26" s="1">
+        <v>23000</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="1">
         <v>3000</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="B27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="1">
-        <v>32000</v>
-      </c>
       <c r="D27" s="1">
-        <v>23000</v>
+        <v>800</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C28" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="D28" s="1">
         <v>800</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="99" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="D29" s="1">
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="99" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C30" s="1">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D30" s="1">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C31" s="1">
+        <v>700</v>
+      </c>
+      <c r="D31" s="1">
+        <v>500</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="1">
+        <v>7500</v>
+      </c>
+      <c r="D32" s="1">
+        <v>5500</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="1">
+        <v>12000</v>
+      </c>
+      <c r="D33" s="1">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="1">
         <v>4000</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D34" s="1">
         <v>2500</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="1">
-        <v>700</v>
-      </c>
-      <c r="D32" s="1">
-        <v>500</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="1">
-        <v>7500</v>
-      </c>
-      <c r="D33" s="1">
-        <v>5500</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" ht="148.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="1">
-        <v>12000</v>
-      </c>
-      <c r="D34" s="1">
-        <v>6000</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="165" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C35" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="D35" s="1">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="66" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1">
-        <v>2000</v>
+        <v>3780</v>
       </c>
       <c r="D36" s="1">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="66" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C37" s="1">
-        <v>3780</v>
+        <v>970</v>
       </c>
       <c r="D37" s="1">
-        <v>1800</v>
+        <v>650</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C38" s="1">
-        <v>970</v>
+        <v>6000</v>
       </c>
       <c r="D38" s="1">
-        <v>650</v>
+        <v>3000</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C39" s="1">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="D39" s="1">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B40" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="1">
-        <v>4800</v>
-      </c>
-      <c r="D40" s="1">
-        <v>3800</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F40" t="s">
         <v>78</v>
       </c>
     </row>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97770519-CD24-4379-8A09-2100E9D8E4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCE819B-3D70-4EA3-9E5A-37D3A5686472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
+    <workbookView xWindow="-24480" yWindow="645" windowWidth="20595" windowHeight="14265" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="143">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -875,14 +875,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Haier 雙層防燙多功能智能美食鍋、附蒸架</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Haier美食鍋.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>義大利Giaretti 復古造型 麵包機 GT-OT10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1001,6 +993,44 @@
   <si>
     <t>需自取(五股衛生所附近)
 全新拆封 發現家裡不適合  已組裝好 免安裝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vios1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vios2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vios3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2005年 vios 1.5E 數位儀表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接手家人另一台車，這台用不到了
+有興趣私訊喊價，不然下週就直接丟車商了XD
+代步、新手練習，好養好顧，
+便利配備都有了，不用在更新
+開個一年之後汰舊換新還可以折5～10萬
+2025 更換項目
+- 四條輪胎(輪胎很新跑沒多少...)
+- Andoid車機(8核32G)，含倒車顯影
+- 行車記錄器
+- 全車更換LED，含排檔燈中控燈 (大燈除外)
+- 重灌冷媒
+2023 更換項目 
+- 重貼隔熱紙
+- 裝電子後視鏡
+里程27快28萬，一手原板件，有一些刮痕
+每半年準時在toyota原廠保養，有紀錄
+原廠列注意項目
+- 右前避震器漏油(不影響安全與行駛)
+- 水箱軟管接口結晶(注意副水箱水量即可，目前自己還沒需要添加過)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1392,7 +1422,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1401,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1410,72 +1440,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3">
+        <v>1600</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" t="s">
         <v>134</v>
       </c>
-      <c r="C2">
-        <v>1600</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H3" t="s">
         <v>135</v>
       </c>
-      <c r="G2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3">
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4">
         <v>650</v>
-      </c>
-      <c r="F3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4">
-        <v>1300</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C5">
-        <v>900</v>
-      </c>
-      <c r="E5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" t="s">
         <v>120</v>
-      </c>
-      <c r="F5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1483,47 +1513,50 @@
         <v>115</v>
       </c>
       <c r="C6">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="F6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
-        <v>133</v>
-      </c>
-      <c r="G7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>0</v>
-      </c>
       <c r="B8" t="s">
         <v>110</v>
       </c>
       <c r="C8">
-        <v>350</v>
+        <v>550</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
       </c>
       <c r="F8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" t="s">
         <v>111</v>
+      </c>
+      <c r="H8" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.25">
@@ -1643,7 +1676,7 @@
         <v>900</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -1988,7 +2021,7 @@
         <v>6000</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F33" t="s">
         <v>62</v>
@@ -2005,7 +2038,7 @@
         <v>2500</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F34" t="s">
         <v>64</v>
@@ -2022,7 +2055,7 @@
         <v>900</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
         <v>66</v>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCE819B-3D70-4EA3-9E5A-37D3A5686472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F484379-2169-4569-8ADC-212F1DB7CDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24480" yWindow="645" windowWidth="20595" windowHeight="14265" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="138">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -429,26 +429,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>POJUN PJ02.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POJUN PJ022.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POJUN PJ023.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POJUN PJ024.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POJUN PJ02 粉白色 機械式鍵盤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>B.FRiEND KB700-Pro 鋁合金薄型鍵盤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -461,353 +441,6 @@
 ●支援雙系統，一鍵切換win/ios
 官方介紹：
 http://www.b-friendit.com/web/product/office_in.jsp?pd_no=PD1605779107279</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>材質</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>鋁合金上蓋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>髮絲紋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>軸承</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:KAILH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>凱華軸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>-5000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>萬次點擊壽命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>顏色搭配</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:38</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>顆粉色鍵帽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>+66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>顆白色鍵帽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>💖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>燈光效果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>:20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>種燈光效果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>+10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>組自訂義</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-🎁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>贈送一套相反配色鍵帽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>自由搭配</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-官方介紹：
-https://www.pojunshop.com/products/pj02-%E7%B2%89%E7%99%BD%E6%A9%9F%E6%A2%B0%E5%BC%8F%E9%8D%B5%E7%9B%A4?srsltid=AfmBOoq4HFZmx_1_BgksTVqIMnXOo4-vfcgdEfCQX6pgq3NC6OzCW24n</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1012,22 +645,30 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>vios4.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>接手家人另一台車，這台用不到了
-有興趣私訊喊價，不然下週就直接丟車商了XD
+有興趣私訊
 代步、新手練習，好養好顧，
-便利配備都有了，不用在更新
-開個一年之後汰舊換新還可以折5～10萬
+便利配備都有了(安卓機、CarPlay、電子後視鏡、倒車顯影、行車記錄器、測速照相偵測)
+開個一年之後汰舊換新也划算！
+都在Toyota原廠保養，有近兩年工單
 2025 更換項目
-- 四條輪胎(輪胎很新跑沒多少...)
+- 四條輪胎(輪胎跑沒多少...)
 - Andoid車機(8核32G)，含倒車顯影
 - 行車記錄器
 - 全車更換LED，含排檔燈中控燈 (大燈除外)
 - 重灌冷媒
+2024 更換項目
+- 電瓶
+- 煞車碟盤
 2023 更換項目 
 - 重貼隔熱紙
 - 裝電子後視鏡
-里程27快28萬，一手原板件，有一些刮痕
-每半年準時在toyota原廠保養，有紀錄
+里程27快28萬
+一手原板件，無重大事故、無泡水，車身有一些刮痕
 原廠列注意項目
 - 右前避震器漏油(不影響安全與行駛)
 - 水箱軟管接口結晶(注意副水箱水量即可，目前自己還沒需要添加過)</t>
@@ -1038,7 +679,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1053,18 +694,6 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1410,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE215CEF-0362-4ABB-BECD-48602F7139CF}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -1422,7 +1051,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1431,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1442,39 +1071,48 @@
     </row>
     <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
+      </c>
+      <c r="C2">
+        <v>88000</v>
+      </c>
+      <c r="D2">
+        <v>68000</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
-        <v>140</v>
+        <v>134</v>
+      </c>
+      <c r="I2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>1600</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1482,650 +1120,627 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C4">
         <v>650</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C5">
         <v>1300</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C6">
         <v>900</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C7">
         <v>400</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C8">
         <v>550</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F8" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C9">
         <v>2800</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C10">
         <v>1500</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="219" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C11">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C12">
         <v>1100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>1100</v>
       </c>
+      <c r="D13">
+        <v>900</v>
+      </c>
       <c r="E13" s="1" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="D14">
+        <v>150</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9000</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="198" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D16" s="1">
         <v>900</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15">
-        <v>300</v>
-      </c>
-      <c r="D15">
-        <v>150</v>
-      </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1">
-        <v>9000</v>
-      </c>
-      <c r="D16" s="1">
-        <v>4500</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="198" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="D17" s="1">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="66" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1">
+        <v>7000</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1">
         <v>1000</v>
       </c>
-      <c r="D18" s="1">
-        <v>700</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="66" x14ac:dyDescent="0.25">
-      <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="1">
-        <v>7000</v>
-      </c>
       <c r="D19" s="1">
-        <v>3500</v>
+        <v>600</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C20" s="1">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D20" s="1">
-        <v>600</v>
+        <v>2500</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>4000</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2500</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="1">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="165" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
+        <v>32000</v>
+      </c>
+      <c r="D25" s="1">
+        <v>23000</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="1">
         <v>3000</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="165" x14ac:dyDescent="0.25">
-      <c r="B26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="1">
-        <v>32000</v>
-      </c>
       <c r="D26" s="1">
-        <v>23000</v>
+        <v>800</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="33" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C27" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="D27" s="1">
         <v>800</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="99" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="D28" s="1">
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="99" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C29" s="1">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="D29" s="1">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C30" s="1">
+        <v>700</v>
+      </c>
+      <c r="D30" s="1">
+        <v>500</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="1">
+        <v>7500</v>
+      </c>
+      <c r="D31" s="1">
+        <v>5500</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="1">
+        <v>12000</v>
+      </c>
+      <c r="D32" s="1">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="165" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="1">
         <v>4000</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D33" s="1">
         <v>2500</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="33" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="1">
-        <v>700</v>
-      </c>
-      <c r="D31" s="1">
-        <v>500</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="1">
-        <v>7500</v>
-      </c>
-      <c r="D32" s="1">
-        <v>5500</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="148.5" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="1">
-        <v>12000</v>
-      </c>
-      <c r="D33" s="1">
-        <v>6000</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" ht="165" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C34" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="D34" s="1">
-        <v>2500</v>
+        <v>900</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="66" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C35" s="1">
-        <v>2000</v>
+        <v>3780</v>
       </c>
       <c r="D35" s="1">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="66" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C36" s="1">
-        <v>3780</v>
+        <v>970</v>
       </c>
       <c r="D36" s="1">
-        <v>1800</v>
+        <v>650</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="33" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1">
-        <v>970</v>
+        <v>6000</v>
       </c>
       <c r="D37" s="1">
-        <v>650</v>
+        <v>3000</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C38" s="1">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="D38" s="1">
-        <v>3000</v>
+        <v>3800</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="1">
-        <v>4800</v>
-      </c>
-      <c r="D39" s="1">
-        <v>3800</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F39" t="s">
         <v>78</v>
       </c>
     </row>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F484379-2169-4569-8ADC-212F1DB7CDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651A80B0-1EF7-479A-843E-5DEDF2E2668E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24480" yWindow="645" windowWidth="20595" windowHeight="14265" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
@@ -1070,6 +1070,9 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>135</v>
       </c>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651A80B0-1EF7-479A-843E-5DEDF2E2668E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99924D76-80A3-4897-B552-63BC36012554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24480" yWindow="645" windowWidth="20595" windowHeight="14265" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
+    <workbookView xWindow="-28920" yWindow="-885" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -1291,7 +1291,7 @@
         <v>1100</v>
       </c>
       <c r="D13">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>131</v>
@@ -1325,7 +1325,7 @@
         <v>9000</v>
       </c>
       <c r="D15" s="1">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>24</v>
@@ -1345,7 +1345,7 @@
         <v>1200</v>
       </c>
       <c r="D16" s="1">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -1362,7 +1362,7 @@
         <v>1000</v>
       </c>
       <c r="D17" s="1">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>40</v>
@@ -1399,7 +1399,7 @@
         <v>1000</v>
       </c>
       <c r="D19" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>39</v>
@@ -1422,7 +1422,7 @@
         <v>4000</v>
       </c>
       <c r="D20" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>39</v>
@@ -1511,7 +1511,7 @@
         <v>32000</v>
       </c>
       <c r="D25" s="1">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>81</v>
@@ -1531,7 +1531,7 @@
         <v>3000</v>
       </c>
       <c r="D26" s="1">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>46</v>
@@ -1565,7 +1565,7 @@
         <v>4500</v>
       </c>
       <c r="D28" s="1">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>55</v>
@@ -1599,7 +1599,7 @@
         <v>700</v>
       </c>
       <c r="D30" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>53</v>
@@ -1619,7 +1619,7 @@
         <v>7500</v>
       </c>
       <c r="D31" s="1">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>77</v>
@@ -1636,7 +1636,7 @@
         <v>12000</v>
       </c>
       <c r="D32" s="1">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>122</v>
@@ -1653,7 +1653,7 @@
         <v>4000</v>
       </c>
       <c r="D33" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>121</v>
@@ -1670,7 +1670,7 @@
         <v>2000</v>
       </c>
       <c r="D34" s="1">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>120</v>
@@ -1687,7 +1687,7 @@
         <v>3780</v>
       </c>
       <c r="D35" s="1">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>67</v>
@@ -1704,7 +1704,7 @@
         <v>970</v>
       </c>
       <c r="D36" s="1">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -1721,7 +1721,7 @@
         <v>6000</v>
       </c>
       <c r="D37" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>73</v>
@@ -1738,7 +1738,7 @@
         <v>4800</v>
       </c>
       <c r="D38" s="1">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>80</v>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99924D76-80A3-4897-B552-63BC36012554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E79D2E5-2D93-44D5-BB8B-B08ABDF3B03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-885" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
+    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="137">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -629,49 +629,48 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>vios1.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vios2.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vios3.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2005年 vios 1.5E 數位儀表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vios4.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>接手家人另一台車，這台用不到了
-有興趣私訊
-代步、新手練習，好養好顧，
-便利配備都有了(安卓機、CarPlay、電子後視鏡、倒車顯影、行車記錄器、測速照相偵測)
-開個一年之後汰舊換新也划算！
-都在Toyota原廠保養，有近兩年工單
-2025 更換項目
-- 四條輪胎(輪胎跑沒多少...)
-- Andoid車機(8核32G)，含倒車顯影
-- 行車記錄器
-- 全車更換LED，含排檔燈中控燈 (大燈除外)
-- 重灌冷媒
-2024 更換項目
-- 電瓶
-- 煞車碟盤
-2023 更換項目 
-- 重貼隔熱紙
-- 裝電子後視鏡
-里程27快28萬
-一手原板件，無重大事故、無泡水，車身有一些刮痕
-原廠列注意項目
-- 右前避震器漏油(不影響安全與行駛)
-- 水箱軟管接口結晶(注意副水箱水量即可，目前自己還沒需要添加過)</t>
+    <r>
+      <t>僅使用一次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，本來要露營用，後來就沒出門了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+真實1080P投影機
+Android 13 開機即看</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOCAJoyLite1.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOCAJoyLite2.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOCAJoyLite3.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOCA Joy Lite 投影機</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -679,7 +678,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -694,6 +693,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1069,33 +1075,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2">
+        <v>2000</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" t="s">
         <v>135</v>
-      </c>
-      <c r="C2">
-        <v>88000</v>
-      </c>
-      <c r="D2">
-        <v>68000</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E79D2E5-2D93-44D5-BB8B-B08ABDF3B03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F0B97-285B-43B5-A263-3853D89A5334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
@@ -624,11 +624,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需自取(五股衛生所附近)
-全新拆封 發現家裡不適合  已組裝好 免安裝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>僅使用一次</t>
     </r>
@@ -671,6 +666,10 @@
   </si>
   <si>
     <t>KOCA Joy Lite 投影機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全新拆封  組裝後發現家裡不適合</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1077,22 +1076,22 @@
     </row>
     <row r="2" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>2000</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" t="s">
         <v>132</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>133</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>134</v>
-      </c>
-      <c r="H2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
@@ -1280,7 +1279,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -1291,7 +1290,7 @@
         <v>800</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>

--- a/data/items.xlsx
+++ b/data/items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\Web\GitHub\testProj\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F0B97-285B-43B5-A263-3853D89A5334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E385567F-78C3-41E6-80FD-3254002A08D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="17520" xr2:uid="{CE2EAC41-46D5-4916-BBDF-65F77E21BC69}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="134">
   <si>
     <t>品項名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -329,19 +329,6 @@
   </si>
   <si>
     <t>DrivePro20機車行車記錄器.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>參考
-https://www.philo.com.tw/item/tp20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHILO TP20 無線電動打氣機</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHILOTP20無線電動打氣機.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1044,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE215CEF-0362-4ABB-BECD-48602F7139CF}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -1056,7 +1043,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1065,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1076,42 +1063,48 @@
     </row>
     <row r="2" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C2">
-        <v>2000</v>
+        <v>2500</v>
+      </c>
+      <c r="D2">
+        <v>1800</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" t="s">
         <v>131</v>
-      </c>
-      <c r="F2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3">
+        <v>2000</v>
+      </c>
+      <c r="D3">
+        <v>1400</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" t="s">
         <v>126</v>
-      </c>
-      <c r="C3">
-        <v>1600</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1119,164 +1112,164 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C4">
         <v>650</v>
       </c>
       <c r="F4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C5">
         <v>1300</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>900</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C7">
         <v>400</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C8">
         <v>550</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C9">
         <v>2800</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="214.5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10">
         <v>1500</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" t="s">
         <v>95</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" t="s">
         <v>97</v>
-      </c>
-      <c r="G10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11">
         <v>1100</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" t="s">
         <v>87</v>
-      </c>
-      <c r="G11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="181.5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>1100</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" t="s">
         <v>83</v>
-      </c>
-      <c r="G12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1290,7 +1283,7 @@
         <v>800</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -1341,7 +1334,7 @@
         <v>1200</v>
       </c>
       <c r="D16" s="1">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -1358,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="D17" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>40</v>
@@ -1381,7 +1374,7 @@
         <v>3500</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -1395,7 +1388,7 @@
         <v>1000</v>
       </c>
       <c r="D19" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>39</v>
@@ -1418,7 +1411,7 @@
         <v>4000</v>
       </c>
       <c r="D20" s="1">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>39</v>
@@ -1507,10 +1500,10 @@
         <v>32000</v>
       </c>
       <c r="D25" s="1">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
         <v>35</v>
@@ -1527,7 +1520,7 @@
         <v>3000</v>
       </c>
       <c r="D26" s="1">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>46</v>
@@ -1581,7 +1574,7 @@
         <v>2500</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
         <v>51</v>
@@ -1618,7 +1611,7 @@
         <v>4500</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
         <v>60</v>
@@ -1635,7 +1628,7 @@
         <v>5000</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
         <v>62</v>
@@ -1652,7 +1645,7 @@
         <v>2000</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s">
         <v>64</v>
@@ -1666,10 +1659,10 @@
         <v>2000</v>
       </c>
       <c r="D34" s="1">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
@@ -1683,7 +1676,7 @@
         <v>3780</v>
       </c>
       <c r="D35" s="1">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>67</v>
@@ -1697,10 +1690,10 @@
         <v>71</v>
       </c>
       <c r="C36" s="1">
-        <v>970</v>
+        <v>6000</v>
       </c>
       <c r="D36" s="1">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>70</v>
@@ -1709,38 +1702,21 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="2:6" ht="33" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C37" s="1">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="D37" s="1">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="1">
-        <v>4800</v>
-      </c>
-      <c r="D38" s="1">
-        <v>3500</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F38" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
